--- a/output/pdf_financials_xlsx/LVX.xlsx
+++ b/output/pdf_financials_xlsx/LVX.xlsx
@@ -720,19 +720,19 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.003009</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.020582</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.125598</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.121427</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.08263</v>
       </c>
     </row>
     <row r="13">
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.962661</v>
+        <v>-4.96567</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.65346</v>
+        <v>-3.674042</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.342959</v>
+        <v>-1.468557</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.357957</v>
+        <v>-1.479384</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.772288</v>
+        <v>-1.854918</v>
       </c>
     </row>
     <row r="28">
@@ -1197,19 +1197,19 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.947288</v>
+        <v>-4.950297</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.585139</v>
+        <v>-3.605721</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.301117</v>
+        <v>-1.426715</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.339573</v>
+        <v>-1.461</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.770895</v>
+        <v>-1.853525</v>
       </c>
     </row>
     <row r="30">
@@ -1327,22 +1327,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>8.17755</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>5.014313</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>3.913925</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.65847</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>3.830711</v>
       </c>
     </row>
     <row r="35">
@@ -1377,22 +1377,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>8.17755</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>5.014313</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>3.913925</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.65847</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>3.830711</v>
       </c>
     </row>
     <row r="37">
@@ -1677,22 +1677,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>8.403461</v>
+        <v>0.225911</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>5.12046</v>
+        <v>0.106147</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>3.98238</v>
+        <v>0.068455</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.730385</v>
+        <v>0.07191500000000001</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.034041</v>
+        <v>0.20333</v>
       </c>
     </row>
     <row r="49">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -9992,7 +9992,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">

--- a/output/pdf_financials_xlsx/LVX.xlsx
+++ b/output/pdf_financials_xlsx/LVX.xlsx
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>1.097868</v>
+        <v>1.129118</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.598357</v>
+        <v>0.673357</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.564537</v>
+        <v>0.589537</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.536402</v>
+        <v>0.581402</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.620336</v>
+        <v>0.657336</v>
       </c>
     </row>
     <row r="8">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.097868</v>
+        <v>1.129118</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>3.674042</v>
@@ -5576,7 +5576,11 @@
           <t>Proceeds from share issuances</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
@@ -8316,7 +8320,11 @@
           <t>Share issued for cash</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E96" s="5" t="n">
         <v>1e-06</v>
       </c>
@@ -8784,7 +8792,11 @@
           <t>Shares issued for cash 1 1 - -</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr"/>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E106" s="5" t="n">
         <v>1e-06</v>
       </c>
@@ -9296,7 +9308,11 @@
           <t>Director fees (Note 9)</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -10240,7 +10256,11 @@
           <t>Director Fees (Note 8)</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E139" t="inlineStr">
         <is>
           <t>-</t>
@@ -10832,7 +10852,11 @@
           <t>Director Fees (Note 9)</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E152" t="inlineStr">
         <is>
           <t>-</t>
